--- a/update-dependencies-fr-core-annuaire/ig/CodeSystem-act-type-ror-codesystem.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/CodeSystem-act-type-ror-codesystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T08:09:55+00:00</t>
+    <t>2026-08-20T16:34:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/update-dependencies-fr-core-annuaire/ig/CodeSystem-act-type-ror-codesystem.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/CodeSystem-act-type-ror-codesystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T16:34:37+00:00</t>
+    <t>2026-08-21T09:28:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/update-dependencies-fr-core-annuaire/ig/CodeSystem-act-type-ror-codesystem.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/CodeSystem-act-type-ror-codesystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T09:28:33+00:00</t>
+    <t>2026-08-21T09:39:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/update-dependencies-fr-core-annuaire/ig/CodeSystem-act-type-ror-codesystem.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/CodeSystem-act-type-ror-codesystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T09:39:43+00:00</t>
+    <t>2026-08-21T14:30:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/update-dependencies-fr-core-annuaire/ig/CodeSystem-act-type-ror-codesystem.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/CodeSystem-act-type-ror-codesystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T14:30:36+00:00</t>
+    <t>2026-08-21T16:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/update-dependencies-fr-core-annuaire/ig/CodeSystem-act-type-ror-codesystem.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/CodeSystem-act-type-ror-codesystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T16:03:39+00:00</t>
+    <t>2026-08-26T13:04:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
